--- a/data/dividends_info_20261017.xlsx
+++ b/data/dividends_info_20261017.xlsx
@@ -1709,7 +1709,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1719,14 +1719,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2025,14 +2025,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2076,14 +2076,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2093,14 +2093,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2110,14 +2110,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2229,14 +2229,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2399,14 +2399,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2416,14 +2416,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2508,7 +2508,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2705,14 +2705,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2756,14 +2756,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2790,14 +2790,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2807,14 +2807,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2916,7 +2916,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3086,7 +3086,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3103,7 +3103,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3232,14 +3232,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3290,7 +3290,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3341,7 +3341,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3402,14 +3402,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3528,7 +3528,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3589,14 +3589,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3861,14 +3861,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3895,14 +3895,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3987,7 +3987,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4004,7 +4004,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4082,14 +4082,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4184,14 +4184,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4201,14 +4201,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4225,7 +4225,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4269,14 +4269,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4293,7 +4293,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4327,7 +4327,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4344,7 +4344,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4412,7 +4412,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4514,7 +4514,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4548,7 +4548,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4711,14 +4711,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4762,14 +4762,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4779,14 +4779,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4871,7 +4871,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4905,7 +4905,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4956,7 +4956,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5000,14 +5000,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5034,14 +5034,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5323,14 +5323,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5364,7 +5364,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5476,14 +5476,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5493,14 +5493,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5748,14 +5748,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5799,14 +5799,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5857,7 +5857,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5980,112 +5980,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EuroGroup Laminations S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>